--- a/day_18/test data/DATA.xlsx
+++ b/day_18/test data/DATA.xlsx
@@ -5,17 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuzur\Desktop\code here only in tests\Playwright\test data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuzur\Desktop\Capgemini_Training_HandsOn_DayWise\day_18\test data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F495BEC3-8868-4F24-B5D4-657033DC2CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0137DB70-81B8-4206-9DC2-3BCAFCB0202E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -497,4 +498,13 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30548B41-8C26-4BC9-BC68-E98D5423DF69}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>